--- a/Datos limpios/Pricing diario/2025/Cebada.xlsx
+++ b/Datos limpios/Pricing diario/2025/Cebada.xlsx
@@ -8487,298 +8487,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100D6CA5EAACE9DA04D9E421A617A76D009" ma:contentTypeVersion="19" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="854b0670eee28d8fa271d4f22cb9c97d">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="77131357-5c03-45fa-a80b-b9111bb46cb1" xmlns:ns3="d3f11db4-a96c-41b4-b8ec-902c72f52048" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b486ba09ce8a2fb19cc660d7edf32df4" ns2:_="" ns3:_="">
-    <xsd:import namespace="77131357-5c03-45fa-a80b-b9111bb46cb1"/>
-    <xsd:import namespace="d3f11db4-a96c-41b4-b8ec-902c72f52048"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:_Flow_SignoffStatus" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="77131357-5c03-45fa-a80b-b9111bb46cb1" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="10" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="11" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="12" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="13" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="14" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="15" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="17" nillable="true" ma:displayName="Location" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="_Flow_SignoffStatus" ma:index="20" nillable="true" ma:displayName="Estado de aprobación" ma:internalName="Estado_x0020_de_x0020_aprobaci_x00f3_n">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="21" nillable="true" ma:displayName="Length (seconds)" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="23" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Etiquetas de imagen" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="6ab20cb4-9c0f-41d2-89f3-02c382a657d6" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="25" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="26" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="d3f11db4-a96c-41b4-b8ec-902c72f52048" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="18" nillable="true" ma:displayName="Compartido con" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="19" nillable="true" ma:displayName="Detalles de uso compartido" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="24" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ac6aff7b-77d9-4645-af3f-7b0008d975fa}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="d3f11db4-a96c-41b4-b8ec-902c72f52048">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de contenido"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_Flow_SignoffStatus xmlns="77131357-5c03-45fa-a80b-b9111bb46cb1" xsi:nil="true"/>
-    <TaxCatchAll xmlns="d3f11db4-a96c-41b4-b8ec-902c72f52048" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="77131357-5c03-45fa-a80b-b9111bb46cb1">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{75BCCBBD-C199-48BF-B4C3-DEF88CEA1AF0}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8D610BE4-1CCB-4D61-BE40-34DFEA472844}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{625EC8D6-C9D5-4C65-A18C-5509193A5453}"/>
 </file>
--- a/Datos limpios/Pricing diario/2025/Cebada.xlsx
+++ b/Datos limpios/Pricing diario/2025/Cebada.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K219"/>
+  <dimension ref="A1:K238"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -8452,33 +8452,736 @@
         <v>45957</v>
       </c>
       <c r="B219">
+        <v>7856.26</v>
+      </c>
+      <c r="C219">
+        <v>0</v>
+      </c>
+      <c r="D219">
+        <v>0</v>
+      </c>
+      <c r="E219">
+        <v>7856.26</v>
+      </c>
+      <c r="F219">
+        <v>11532.08</v>
+      </c>
+      <c r="G219">
+        <v>0</v>
+      </c>
+      <c r="H219">
+        <v>0</v>
+      </c>
+      <c r="I219">
+        <v>11532.08</v>
+      </c>
+      <c r="J219">
+        <v>19388.34</v>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="2">
+        <v>45958</v>
+      </c>
+      <c r="B220">
+        <v>10205.26</v>
+      </c>
+      <c r="C220">
+        <v>0</v>
+      </c>
+      <c r="D220">
+        <v>0</v>
+      </c>
+      <c r="E220">
+        <v>10205.26</v>
+      </c>
+      <c r="F220">
+        <v>8016</v>
+      </c>
+      <c r="G220">
+        <v>0</v>
+      </c>
+      <c r="H220">
+        <v>0</v>
+      </c>
+      <c r="I220">
+        <v>8016</v>
+      </c>
+      <c r="J220">
+        <v>18221.26</v>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="2">
+        <v>45959</v>
+      </c>
+      <c r="B221">
+        <v>10783</v>
+      </c>
+      <c r="C221">
+        <v>1030</v>
+      </c>
+      <c r="D221">
+        <v>340</v>
+      </c>
+      <c r="E221">
+        <v>11473</v>
+      </c>
+      <c r="F221">
+        <v>300</v>
+      </c>
+      <c r="G221">
+        <v>0</v>
+      </c>
+      <c r="H221">
+        <v>0</v>
+      </c>
+      <c r="I221">
+        <v>300</v>
+      </c>
+      <c r="J221">
+        <v>11773</v>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="2">
+        <v>45960</v>
+      </c>
+      <c r="B222">
+        <v>18056.23</v>
+      </c>
+      <c r="C222">
+        <v>0</v>
+      </c>
+      <c r="D222">
+        <v>0</v>
+      </c>
+      <c r="E222">
+        <v>18056.23</v>
+      </c>
+      <c r="F222">
+        <v>3480</v>
+      </c>
+      <c r="G222">
+        <v>0</v>
+      </c>
+      <c r="H222">
+        <v>0</v>
+      </c>
+      <c r="I222">
+        <v>3480</v>
+      </c>
+      <c r="J222">
+        <v>21536.23</v>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="2">
+        <v>45961</v>
+      </c>
+      <c r="B223">
+        <v>30580</v>
+      </c>
+      <c r="C223">
+        <v>0</v>
+      </c>
+      <c r="D223">
+        <v>150</v>
+      </c>
+      <c r="E223">
+        <v>30430</v>
+      </c>
+      <c r="F223">
+        <v>930</v>
+      </c>
+      <c r="G223">
+        <v>0</v>
+      </c>
+      <c r="H223">
+        <v>0</v>
+      </c>
+      <c r="I223">
+        <v>930</v>
+      </c>
+      <c r="J223">
+        <v>31360</v>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="2">
+        <v>45964</v>
+      </c>
+      <c r="B224">
+        <v>26005.8</v>
+      </c>
+      <c r="C224">
+        <v>0</v>
+      </c>
+      <c r="D224">
+        <v>0</v>
+      </c>
+      <c r="E224">
+        <v>26005.8</v>
+      </c>
+      <c r="F224">
         <v>450</v>
       </c>
-      <c r="C219">
-        <v>0</v>
-      </c>
-      <c r="D219">
-        <v>0</v>
-      </c>
-      <c r="E219">
+      <c r="G224">
+        <v>0</v>
+      </c>
+      <c r="H224">
+        <v>0</v>
+      </c>
+      <c r="I224">
         <v>450</v>
       </c>
-      <c r="F219">
-        <v>7500</v>
-      </c>
-      <c r="G219">
-        <v>0</v>
-      </c>
-      <c r="H219">
-        <v>0</v>
-      </c>
-      <c r="I219">
-        <v>7500</v>
-      </c>
-      <c r="J219">
-        <v>7950</v>
-      </c>
-      <c r="K219" t="inlineStr">
+      <c r="J224">
+        <v>26455.8</v>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="2">
+        <v>45965</v>
+      </c>
+      <c r="B225">
+        <v>8770</v>
+      </c>
+      <c r="C225">
+        <v>0</v>
+      </c>
+      <c r="D225">
+        <v>0</v>
+      </c>
+      <c r="E225">
+        <v>8770</v>
+      </c>
+      <c r="F225">
+        <v>32590.76</v>
+      </c>
+      <c r="G225">
+        <v>0</v>
+      </c>
+      <c r="H225">
+        <v>0</v>
+      </c>
+      <c r="I225">
+        <v>32590.76</v>
+      </c>
+      <c r="J225">
+        <v>41360.75999999999</v>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="2">
+        <v>45966</v>
+      </c>
+      <c r="B226">
+        <v>20645.77</v>
+      </c>
+      <c r="C226">
+        <v>0</v>
+      </c>
+      <c r="D226">
+        <v>0</v>
+      </c>
+      <c r="E226">
+        <v>20645.77</v>
+      </c>
+      <c r="F226">
+        <v>27.88</v>
+      </c>
+      <c r="G226">
+        <v>0</v>
+      </c>
+      <c r="H226">
+        <v>0</v>
+      </c>
+      <c r="I226">
+        <v>27.88</v>
+      </c>
+      <c r="J226">
+        <v>20673.65</v>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="2">
+        <v>45967</v>
+      </c>
+      <c r="B227">
+        <v>12972.76</v>
+      </c>
+      <c r="C227">
+        <v>0</v>
+      </c>
+      <c r="D227">
+        <v>2000</v>
+      </c>
+      <c r="E227">
+        <v>10972.76</v>
+      </c>
+      <c r="F227">
+        <v>1320</v>
+      </c>
+      <c r="G227">
+        <v>0</v>
+      </c>
+      <c r="H227">
+        <v>0</v>
+      </c>
+      <c r="I227">
+        <v>1320</v>
+      </c>
+      <c r="J227">
+        <v>12292.76</v>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="2">
+        <v>45968</v>
+      </c>
+      <c r="B228">
+        <v>16406.74</v>
+      </c>
+      <c r="C228">
+        <v>0</v>
+      </c>
+      <c r="D228">
+        <v>0</v>
+      </c>
+      <c r="E228">
+        <v>16406.74</v>
+      </c>
+      <c r="F228">
+        <v>7378.32</v>
+      </c>
+      <c r="G228">
+        <v>0</v>
+      </c>
+      <c r="H228">
+        <v>0</v>
+      </c>
+      <c r="I228">
+        <v>7378.32</v>
+      </c>
+      <c r="J228">
+        <v>23785.06</v>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="2">
+        <v>45971</v>
+      </c>
+      <c r="B229">
+        <v>14869.99</v>
+      </c>
+      <c r="C229">
+        <v>60</v>
+      </c>
+      <c r="D229">
+        <v>280</v>
+      </c>
+      <c r="E229">
+        <v>14649.99</v>
+      </c>
+      <c r="F229">
+        <v>150</v>
+      </c>
+      <c r="G229">
+        <v>0</v>
+      </c>
+      <c r="H229">
+        <v>0</v>
+      </c>
+      <c r="I229">
+        <v>150</v>
+      </c>
+      <c r="J229">
+        <v>14799.99</v>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="2">
+        <v>45972</v>
+      </c>
+      <c r="B230">
+        <v>21980.6</v>
+      </c>
+      <c r="C230">
+        <v>0</v>
+      </c>
+      <c r="D230">
+        <v>0</v>
+      </c>
+      <c r="E230">
+        <v>21980.6</v>
+      </c>
+      <c r="F230">
+        <v>80</v>
+      </c>
+      <c r="G230">
+        <v>0</v>
+      </c>
+      <c r="H230">
+        <v>0</v>
+      </c>
+      <c r="I230">
+        <v>80</v>
+      </c>
+      <c r="J230">
+        <v>22060.6</v>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="2">
+        <v>45973</v>
+      </c>
+      <c r="B231">
+        <v>10611.56</v>
+      </c>
+      <c r="C231">
+        <v>0</v>
+      </c>
+      <c r="D231">
+        <v>130</v>
+      </c>
+      <c r="E231">
+        <v>10481.56</v>
+      </c>
+      <c r="F231">
+        <v>0</v>
+      </c>
+      <c r="G231">
+        <v>0</v>
+      </c>
+      <c r="H231">
+        <v>0</v>
+      </c>
+      <c r="I231">
+        <v>0</v>
+      </c>
+      <c r="J231">
+        <v>10481.56</v>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="2">
+        <v>45974</v>
+      </c>
+      <c r="B232">
+        <v>15739.25</v>
+      </c>
+      <c r="C232">
+        <v>0</v>
+      </c>
+      <c r="D232">
+        <v>0</v>
+      </c>
+      <c r="E232">
+        <v>15739.25</v>
+      </c>
+      <c r="F232">
+        <v>0</v>
+      </c>
+      <c r="G232">
+        <v>0</v>
+      </c>
+      <c r="H232">
+        <v>0</v>
+      </c>
+      <c r="I232">
+        <v>0</v>
+      </c>
+      <c r="J232">
+        <v>15739.25</v>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="2">
+        <v>45975</v>
+      </c>
+      <c r="B233">
+        <v>12582.57</v>
+      </c>
+      <c r="C233">
+        <v>2000</v>
+      </c>
+      <c r="D233">
+        <v>0</v>
+      </c>
+      <c r="E233">
+        <v>14582.57</v>
+      </c>
+      <c r="F233">
+        <v>40</v>
+      </c>
+      <c r="G233">
+        <v>0</v>
+      </c>
+      <c r="H233">
+        <v>0</v>
+      </c>
+      <c r="I233">
+        <v>40</v>
+      </c>
+      <c r="J233">
+        <v>14622.57</v>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="2">
+        <v>45978</v>
+      </c>
+      <c r="B234">
+        <v>17610.74</v>
+      </c>
+      <c r="C234">
+        <v>0</v>
+      </c>
+      <c r="D234">
+        <v>60</v>
+      </c>
+      <c r="E234">
+        <v>17550.74</v>
+      </c>
+      <c r="F234">
+        <v>14198</v>
+      </c>
+      <c r="G234">
+        <v>0</v>
+      </c>
+      <c r="H234">
+        <v>0</v>
+      </c>
+      <c r="I234">
+        <v>14198</v>
+      </c>
+      <c r="J234">
+        <v>31748.74</v>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="2">
+        <v>45979</v>
+      </c>
+      <c r="B235">
+        <v>28003.37</v>
+      </c>
+      <c r="C235">
+        <v>0</v>
+      </c>
+      <c r="D235">
+        <v>1000</v>
+      </c>
+      <c r="E235">
+        <v>27003.37</v>
+      </c>
+      <c r="F235">
+        <v>420</v>
+      </c>
+      <c r="G235">
+        <v>0</v>
+      </c>
+      <c r="H235">
+        <v>0</v>
+      </c>
+      <c r="I235">
+        <v>420</v>
+      </c>
+      <c r="J235">
+        <v>27423.37</v>
+      </c>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="2">
+        <v>45980</v>
+      </c>
+      <c r="B236">
+        <v>25271</v>
+      </c>
+      <c r="C236">
+        <v>0</v>
+      </c>
+      <c r="D236">
+        <v>0</v>
+      </c>
+      <c r="E236">
+        <v>25271</v>
+      </c>
+      <c r="F236">
+        <v>1785</v>
+      </c>
+      <c r="G236">
+        <v>0</v>
+      </c>
+      <c r="H236">
+        <v>0</v>
+      </c>
+      <c r="I236">
+        <v>1785</v>
+      </c>
+      <c r="J236">
+        <v>27056</v>
+      </c>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="2">
+        <v>45981</v>
+      </c>
+      <c r="B237">
+        <v>26505.74</v>
+      </c>
+      <c r="C237">
+        <v>2200</v>
+      </c>
+      <c r="D237">
+        <v>300</v>
+      </c>
+      <c r="E237">
+        <v>28405.74</v>
+      </c>
+      <c r="F237">
+        <v>1010</v>
+      </c>
+      <c r="G237">
+        <v>0</v>
+      </c>
+      <c r="H237">
+        <v>0</v>
+      </c>
+      <c r="I237">
+        <v>1010</v>
+      </c>
+      <c r="J237">
+        <v>29415.74</v>
+      </c>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="2">
+        <v>45982</v>
+      </c>
+      <c r="B238">
+        <v>10210</v>
+      </c>
+      <c r="C238">
+        <v>0</v>
+      </c>
+      <c r="D238">
+        <v>0</v>
+      </c>
+      <c r="E238">
+        <v>10210</v>
+      </c>
+      <c r="F238">
+        <v>0</v>
+      </c>
+      <c r="G238">
+        <v>0</v>
+      </c>
+      <c r="H238">
+        <v>0</v>
+      </c>
+      <c r="I238">
+        <v>0</v>
+      </c>
+      <c r="J238">
+        <v>10210</v>
+      </c>
+      <c r="K238" t="inlineStr">
         <is>
           <t>CEBADA</t>
         </is>
